--- a/scenarios/testszenario/ferigeSegmentierungParameter.xlsx
+++ b/scenarios/testszenario/ferigeSegmentierungParameter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lel/IdeaProjects/matsim-example-project/scenarios/testszenario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lel/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAED48FC-FE80-4940-BFDC-B3D2B7F1E496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C819C00-91F6-5246-8DD4-E547B5B8F1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="680" windowWidth="20700" windowHeight="21460" xr2:uid="{9607306B-5BD0-464C-922F-AC958A701ECA}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="22500" windowHeight="21460" xr2:uid="{9607306B-5BD0-464C-922F-AC958A701ECA}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Cluster 1: Der multioptionale Urbanist</t>
   </si>
@@ -63,12 +63,6 @@
   </si>
   <si>
     <t>Cluster 8: Der Ländliche</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>o*_l</t>
   </si>
   <si>
     <t>M</t>
@@ -222,7 +216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -306,12 +300,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -332,10 +346,27 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -354,22 +385,13 @@
     <xf numFmtId="10" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -737,224 +759,219 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="18" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="18" t="s">
+      <c r="I1" s="12"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="19"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="18" t="s">
+      <c r="L1" s="12"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="18" t="s">
+      <c r="O1" s="12"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="19"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="18" t="s">
+      <c r="R1" s="12"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="18" t="s">
+      <c r="U1" s="12"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="13"/>
+      <c r="AA1" s="2"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="N2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="Q2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="T2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="W2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="AA2" s="2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="21">
+        <v>11</v>
+      </c>
+      <c r="B3" s="14">
         <v>2244</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="21">
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="14">
         <v>21892</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="21">
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="14">
         <v>16314</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="21">
+      <c r="I3" s="15"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="14">
         <v>5416</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="21">
+      <c r="L3" s="15"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="14">
         <v>8992</v>
       </c>
-      <c r="O3" s="22"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="21">
+      <c r="O3" s="15"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="14">
         <v>4001</v>
       </c>
-      <c r="R3" s="22"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="21">
+      <c r="R3" s="15"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="14">
         <v>10425</v>
       </c>
-      <c r="U3" s="22"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="21">
+      <c r="U3" s="15"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="14">
         <v>17214</v>
       </c>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="23"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="16"/>
       <c r="AA3" s="2"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="15">
+        <v>12</v>
+      </c>
+      <c r="B4" s="20">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="12">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="17">
         <v>0.25309999999999999</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="12">
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="17">
         <v>0.18859999999999999</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="15">
+      <c r="I4" s="18"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="12">
+      <c r="L4" s="21"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="17">
         <v>0.104</v>
       </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="15">
+      <c r="O4" s="18"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="20">
         <v>4.6300000000000001E-2</v>
       </c>
-      <c r="R4" s="16"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="12">
+      <c r="R4" s="21"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="17">
         <v>0.1205</v>
       </c>
-      <c r="U4" s="13"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="12">
+      <c r="U4" s="18"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="17">
         <v>0.19900000000000001</v>
       </c>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="14"/>
+      <c r="X4" s="18"/>
+      <c r="Y4" s="19"/>
       <c r="AA4" s="2"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="7">
         <v>0.61</v>
@@ -963,7 +980,7 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7">
         <v>-0.42</v>
@@ -972,7 +989,7 @@
         <v>0.91</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H5" s="7">
         <v>0.34</v>
@@ -981,7 +998,7 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K5" s="7">
         <v>-0.02</v>
@@ -990,7 +1007,7 @@
         <v>0.97</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N5" s="7">
         <v>0.28999999999999998</v>
@@ -999,7 +1016,7 @@
         <v>0.95</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="7">
         <v>0.19</v>
@@ -1008,7 +1025,7 @@
         <v>0.99</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T5" s="7">
         <v>-0.37</v>
@@ -1017,7 +1034,7 @@
         <v>1.02</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W5" s="7">
         <v>0.17</v>
@@ -1026,13 +1043,13 @@
         <v>0.88</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA5" s="2"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="7">
         <v>0.68</v>
@@ -1041,7 +1058,7 @@
         <v>1.02</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="7">
         <v>-0.37</v>
@@ -1050,7 +1067,7 @@
         <v>0.66</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H6" s="7">
         <v>0.81</v>
@@ -1059,7 +1076,7 @@
         <v>1.01</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K6" s="7">
         <v>0.96</v>
@@ -1068,7 +1085,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N6" s="7">
         <v>-0.23</v>
@@ -1077,7 +1094,7 @@
         <v>0.84</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="7">
         <v>-0.03</v>
@@ -1086,7 +1103,7 @@
         <v>0.91</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T6" s="7">
         <v>-0.24</v>
@@ -1095,7 +1112,7 @@
         <v>0.9</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W6" s="7">
         <v>-0.42</v>
@@ -1104,13 +1121,13 @@
         <v>0.72</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA6" s="2"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" s="7">
         <v>5.75</v>
@@ -1119,7 +1136,7 @@
         <v>1.93</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="7">
         <v>-0.16</v>
@@ -1128,7 +1145,7 @@
         <v>0.12</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="7">
         <v>-0.11</v>
@@ -1137,7 +1154,7 @@
         <v>0.08</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K7" s="7">
         <v>-0.15</v>
@@ -1146,7 +1163,7 @@
         <v>0.16</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N7" s="7">
         <v>-0.15</v>
@@ -1155,7 +1172,7 @@
         <v>0.22</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q7" s="7">
         <v>-0.13</v>
@@ -1164,7 +1181,7 @@
         <v>0.3</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T7" s="7">
         <v>-0.16</v>
@@ -1173,7 +1190,7 @@
         <v>0.12</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W7" s="7">
         <v>-0.19</v>
@@ -1182,13 +1199,13 @@
         <v>0.18</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA7" s="2"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="7">
         <v>-0.19</v>
@@ -1197,7 +1214,7 @@
         <v>0.95</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="7">
         <v>0.24</v>
@@ -1206,7 +1223,7 @@
         <v>0.59</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" s="7">
         <v>-0.13</v>
@@ -1215,7 +1232,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K8" s="7">
         <v>-2.61</v>
@@ -1224,7 +1241,7 @@
         <v>1.23</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N8" s="7">
         <v>0.19</v>
@@ -1233,7 +1250,7 @@
         <v>0.71</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="7">
         <v>0.13</v>
@@ -1242,7 +1259,7 @@
         <v>0.72</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T8" s="7">
         <v>0.23</v>
@@ -1251,7 +1268,7 @@
         <v>0.68</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W8" s="7">
         <v>0.41</v>
@@ -1260,502 +1277,405 @@
         <v>0.5</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <f>B$5*$Z9</f>
-        <v>0.30499999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="2">
-        <f>$AA9</f>
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="E9">
-        <f>E5*$Z9</f>
-        <v>-0.21</v>
+        <v>1</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="25">
+        <v>-0.3</v>
       </c>
       <c r="F9" s="2">
-        <f>$AA9</f>
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="H9">
-        <f>H5*$Z9</f>
-        <v>0.17</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="K9">
-        <f>K5*$Z9</f>
-        <v>-0.01</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="N9">
-        <f>N5*$Z9</f>
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="Q9">
-        <f>Q5*$Z9</f>
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="R9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="T9">
-        <f>T5*$Z9</f>
-        <v>-0.185</v>
-      </c>
-      <c r="U9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="W9">
-        <f>W5*$Z9</f>
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="X9" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="25">
         <v>0.5</v>
       </c>
-      <c r="AA9" s="2">
-        <f>SQRT(1-Z9^2)</f>
-        <v>0.8660254037844386</v>
-      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+      <c r="T9" s="25">
+        <v>-0.6</v>
+      </c>
+      <c r="U9" s="2">
+        <v>1</v>
+      </c>
+      <c r="W9" s="25">
+        <v>-0.2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <f>B$5*$Z10</f>
-        <v>0.27450000000000002</v>
+      <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="24">
+        <v>0.7</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" ref="C10:C15" si="0">$AA10</f>
-        <v>0.89302855497458755</v>
-      </c>
-      <c r="E10">
-        <f>E$5*$Z10</f>
-        <v>-0.189</v>
+        <v>1</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="25">
+        <v>-0.5</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" ref="F10:F14" si="1">$AA10</f>
-        <v>0.89302855497458755</v>
-      </c>
-      <c r="H10">
-        <f>H$5*$Z10</f>
-        <v>0.15300000000000002</v>
-      </c>
-      <c r="I10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="K10">
-        <f>K$5*$Z10</f>
-        <v>-9.0000000000000011E-3</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="N10">
-        <f>N$5*$Z10</f>
-        <v>0.1305</v>
-      </c>
-      <c r="O10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="Q10">
-        <f>Q$5*$Z10</f>
-        <v>8.5500000000000007E-2</v>
-      </c>
-      <c r="R10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="T10">
-        <f>T$5*$Z10</f>
-        <v>-0.16650000000000001</v>
-      </c>
-      <c r="U10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="W10">
-        <f>W$5*$Z10</f>
-        <v>7.6500000000000012E-2</v>
-      </c>
-      <c r="X10" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="Z10">
-        <v>0.45</v>
-      </c>
-      <c r="AA10" s="2">
-        <f t="shared" ref="AA10:AA15" si="2">SQRT(1-Z10^2)</f>
-        <v>0.89302855497458755</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H10" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1</v>
+      </c>
+      <c r="T10" s="25">
+        <v>-0.7</v>
+      </c>
+      <c r="U10" s="2">
+        <v>1</v>
+      </c>
+      <c r="W10" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="X10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
-        <f>B$5*$Z11</f>
-        <v>0.24399999999999999</v>
+        <v>18</v>
+      </c>
+      <c r="B11" s="24">
+        <v>0.75</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
-        <v>0.91651513899116799</v>
-      </c>
-      <c r="E11">
-        <f>E$5*$Z11</f>
-        <v>-0.16800000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="D11" s="23"/>
+      <c r="E11" s="25">
+        <v>-0.3</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>0.91651513899116799</v>
-      </c>
-      <c r="H11">
-        <f>H$5*$Z11</f>
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="K11">
-        <f>K$5*$Z11</f>
-        <v>-8.0000000000000002E-3</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="N11">
-        <f>N$5*$Z11</f>
-        <v>0.11599999999999999</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="Q11">
-        <f>Q$5*$Z11</f>
-        <v>7.6000000000000012E-2</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="T11">
-        <f>T$5*$Z11</f>
-        <v>-0.14799999999999999</v>
-      </c>
-      <c r="U11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="W11">
-        <f>W$5*$Z11</f>
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="X11" s="10">
-        <v>0.92</v>
-      </c>
-      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="25">
         <v>0.4</v>
       </c>
-      <c r="AA11" s="2">
-        <f t="shared" si="2"/>
-        <v>0.91651513899116799</v>
-      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="25">
+        <v>-0.5</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1</v>
+      </c>
+      <c r="W11" s="25">
+        <v>-0.1</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <f>B$5*$Z12</f>
-        <v>0.2135</v>
+      <c r="A12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="24">
+        <v>0.3</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="0"/>
-        <v>0.93674969975975975</v>
-      </c>
-      <c r="E12">
-        <f>E$5*$Z12</f>
-        <v>-0.14699999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="25">
+        <v>0.6</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>0.93674969975975975</v>
-      </c>
-      <c r="H12">
-        <f>H$5*$Z12</f>
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="K12">
-        <f>K$5*$Z12</f>
-        <v>-6.9999999999999993E-3</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="N12">
-        <f>N$5*$Z12</f>
-        <v>0.10149999999999999</v>
-      </c>
-      <c r="O12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="Q12">
-        <f>Q$5*$Z12</f>
-        <v>6.649999999999999E-2</v>
-      </c>
-      <c r="R12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="T12">
-        <f>T$5*$Z12</f>
-        <v>-0.1295</v>
-      </c>
-      <c r="U12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="W12">
-        <f>W$5*$Z12</f>
-        <v>5.9499999999999997E-2</v>
-      </c>
-      <c r="X12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="Z12">
-        <v>0.35</v>
-      </c>
-      <c r="AA12" s="2">
-        <f t="shared" si="2"/>
-        <v>0.93674969975975975</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H12" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="25">
+        <v>0.7</v>
+      </c>
+      <c r="O12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+      <c r="T12" s="25">
+        <v>0.8</v>
+      </c>
+      <c r="U12" s="2">
+        <v>1</v>
+      </c>
+      <c r="W12" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="X12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <f>B$5*$Z13</f>
-        <v>-0.2135</v>
+        <v>20</v>
+      </c>
+      <c r="B13" s="24">
+        <v>-0.6</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="0"/>
-        <v>0.93674969975975975</v>
-      </c>
-      <c r="E13">
-        <f>E$5*$Z13</f>
-        <v>0.14699999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="25">
+        <v>0.4</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="1"/>
-        <v>0.93674969975975975</v>
-      </c>
-      <c r="H13">
-        <f>H$5*$Z13</f>
-        <v>-0.11899999999999999</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="K13">
-        <f>K$5*$Z13</f>
-        <v>6.9999999999999993E-3</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="N13">
-        <f>N$5*$Z13</f>
-        <v>-0.10149999999999999</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="Q13">
-        <f>Q$5*$Z13</f>
-        <v>-6.649999999999999E-2</v>
-      </c>
-      <c r="R13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="T13">
-        <f>T$5*$Z13</f>
-        <v>0.1295</v>
-      </c>
-      <c r="U13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="W13">
-        <f>W$5*$Z13</f>
-        <v>-5.9499999999999997E-2</v>
-      </c>
-      <c r="X13" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="Z13">
-        <v>-0.35</v>
-      </c>
-      <c r="AA13" s="2">
-        <f t="shared" si="2"/>
-        <v>0.93674969975975975</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H13" s="25">
+        <v>-0.3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>-0.2</v>
+      </c>
+      <c r="R13" s="2">
+        <v>1</v>
+      </c>
+      <c r="T13" s="25">
+        <v>0.7</v>
+      </c>
+      <c r="U13" s="2">
+        <v>1</v>
+      </c>
+      <c r="W13" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14">
-        <f>B$5*$Z14</f>
-        <v>0.183</v>
+        <v>21</v>
+      </c>
+      <c r="B14" s="24">
+        <v>0.7</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="0"/>
-        <v>0.95393920141694566</v>
-      </c>
-      <c r="E14">
-        <f>E$5*$Z14</f>
-        <v>-0.126</v>
+        <v>1</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="25">
+        <v>-0.2</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="1"/>
-        <v>0.95393920141694566</v>
-      </c>
-      <c r="H14">
-        <f>H$5*$Z14</f>
-        <v>0.10200000000000001</v>
-      </c>
-      <c r="I14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="K14">
-        <f>K$5*$Z14</f>
-        <v>-6.0000000000000001E-3</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="N14">
-        <f>N$5*$Z14</f>
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="O14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="Q14">
-        <f>Q$5*$Z14</f>
-        <v>5.6999999999999995E-2</v>
-      </c>
-      <c r="R14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="T14">
-        <f>T$5*$Z14</f>
-        <v>-0.111</v>
-      </c>
-      <c r="U14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="W14">
-        <f>W$5*$Z14</f>
-        <v>5.1000000000000004E-2</v>
-      </c>
-      <c r="X14" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="Z14">
-        <v>0.3</v>
-      </c>
-      <c r="AA14" s="2">
-        <f t="shared" si="2"/>
-        <v>0.95393920141694566</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="25">
+        <v>-0.1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1</v>
+      </c>
+      <c r="T14" s="25">
+        <v>-0.7</v>
+      </c>
+      <c r="U14" s="2">
+        <v>1</v>
+      </c>
+      <c r="W14" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="X14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <f>B$5*$Z15</f>
-        <v>0.1525</v>
+      <c r="A15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="24">
+        <v>0.8</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="0"/>
-        <v>0.96824583655185426</v>
-      </c>
-      <c r="E15">
-        <f>E$5*$Z15</f>
-        <v>-0.105</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="25">
+        <v>-0.4</v>
       </c>
       <c r="F15" s="2">
-        <f>$AA15</f>
-        <v>0.96824583655185426</v>
-      </c>
-      <c r="H15">
-        <f>H$5*$Z15</f>
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="K15">
-        <f>K$5*$Z15</f>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="N15">
-        <f>N$5*$Z15</f>
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="Q15">
-        <f>Q$5*$Z15</f>
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="R15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="T15">
-        <f>T$5*$Z15</f>
-        <v>-9.2499999999999999E-2</v>
-      </c>
-      <c r="U15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="W15">
-        <f>W$5*$Z15</f>
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="X15" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="Z15">
-        <v>0.25</v>
-      </c>
-      <c r="AA15" s="2">
-        <f t="shared" si="2"/>
-        <v>0.96824583655185426</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="N15" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="O15" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="T15" s="25">
+        <v>-0.5</v>
+      </c>
+      <c r="U15" s="2">
+        <v>1</v>
+      </c>
+      <c r="W15" s="25">
+        <v>-0.6</v>
+      </c>
+      <c r="X15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:S4"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="B3:D3"/>
@@ -1772,14 +1692,6 @@
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="T4:V4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
